--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,18 +74,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java 驱动datasource部分函数命名不准确：close,com.sequoiadb.base::SequoiadbOption(与com.sequoiadb.net::ConfigOptions命名不符)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015.03.04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>2015.03.04</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>低</t>
-  </si>
-  <si>
-    <t>2.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>未开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -94,7 +115,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -224,13 +245,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -602,34 +623,48 @@
         <v>13</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="8"/>
       <c r="K2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="81">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="11"/>
+      <c r="K3" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,11 +86,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>谭钊波</t>
+    <t>2015.03.04</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2015.03.04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java 驱动部分接口(如Query),存在string和BSONObj两个版本，照成二义性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -107,6 +119,10 @@
   </si>
   <si>
     <t>2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c++ 驱动应该不对外显示_sdb之类的类</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,10 +639,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>15</v>
@@ -648,51 +664,79 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="8"/>
       <c r="K3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="40.5">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="5"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="11"/>
+      <c r="K4" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+    <row r="5" spans="1:12" ht="27">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="11"/>
+      <c r="K5" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="L5" s="5"/>
     </row>
     <row r="6" spans="1:12">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,6 +123,30 @@
   </si>
   <si>
     <t>c++ 驱动应该不对外显示_sdb之类的类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>除C/C++外，其他驱动应该去除存储过程相关的接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015.03.04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -720,37 +744,51 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="8"/>
       <c r="K5" s="11" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+    <row r="6" spans="1:12" ht="27">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="8"/>
-      <c r="K6" s="11"/>
+      <c r="K6" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB内部TODO列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="115">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -547,6 +547,12 @@
     <t>SEQUOIADBMAINSTREAM-317</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>sdb中的js支持并发能力；
+位置命令参数支持nodename；
+delete conf/update conf通过参数控制返回具体的错误参数名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1198,7 +1204,7 @@
       </c>
       <c r="M6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="148.5">
+    <row r="7" spans="1:13" ht="94.5">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1223,7 +1229,7 @@
       <c r="L7" s="11"/>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="40.5">
+    <row r="8" spans="1:13" ht="27">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1294,7 +1300,7 @@
       <c r="L10" s="11"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="202.5">
+    <row r="11" spans="1:13" ht="121.5">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1369,7 +1375,7 @@
       <c r="L13" s="11"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" ht="27">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1419,7 +1425,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13" ht="40.5">
+    <row r="16" spans="1:13" ht="27">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1469,7 +1475,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:13" ht="108">
+    <row r="18" spans="1:13" ht="67.5">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1494,7 +1500,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="1:13" ht="67.5">
+    <row r="19" spans="1:13" ht="40.5">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1519,7 +1525,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="5"/>
     </row>
-    <row r="20" spans="1:13" ht="337.5">
+    <row r="20" spans="1:13" ht="216">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1867,9 +1873,13 @@
       <c r="L33" s="11"/>
       <c r="M33" s="5"/>
     </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+    <row r="34" spans="1:13" ht="54">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
